--- a/output/2026-08-31_12_Italia_Toscana_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-08-31_12_Italia_Toscana_Componentistica_Ventilazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Attiva dal 1979, P.IVA 00267180974, sede Via dell'Agricoltura 27/29/31, Montemurlo (PO). Verificata tramite WebSearch (Kompass, misterimprese, sito ufficiale) - telefono confermato da fonte indipendente.</t>
+          <t>Attiva dal 1979, P.IVA 00267180974, sede Via dell'Agricoltura 27/29/31, Montemurlo (PO). Verificata tramite WebSearch (Kompass, misterimprese, sito ufficiale) - telefono confermato da fonte indipendente. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,10 +536,9 @@
           <t>055 898001</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>P.IVA 05792470485, fondata 2007/2008, 20-49 dipendenti. Telefono principale confermato; ulteriori numeri (055 898005 / 055 0941223) ed email non confermati da fonte indipendente - da ricontrollare. Possibile componente business anche HORECA.</t>
+          <t>P.IVA 05792470485, fondata 2007/2008, 20-49 dipendenti. Telefono principale confermato; ulteriori numeri (055 898005 / 055 0941223) ed email non confermati da fonte indipendente - da ricontrollare. Possibile componente business anche HORECA. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sede Via Trasimeno 3, Prato. Verificata tramite sito ufficiale e directory, forte coerenza col target.</t>
+          <t>Sede Via Trasimeno 3, Prato. Verificata tramite sito ufficiale e directory, forte coerenza col target. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -616,10 +615,9 @@
           <t>+39 0574 25801</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sede Via per le Case Nuove 105, Prato; fondata 2005, 20-49 dipendenti. Telefono/email non confermati da fonte indipendente nei risultati - azienda e sito verificati.</t>
+          <t>Sede Via per le Case Nuove 105, Prato; fondata 2005, 20-49 dipendenti. Telefono/email non confermati da fonte indipendente nei risultati - azienda e sito verificati. [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -738,7 +736,6 @@
           <t>+39 055 9155082</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>P.IVA 01805360482, attiva dal 1981. ATTENZIONE: fonti indicano attività anche su condizionamento/pompe di calore per uso residenziale - verificare la reale quota di business industriale.</t>
@@ -783,7 +780,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>P.IVA 01118460474, 10-19 dipendenti. Indirizzo e telefono confermati da fonte indipendente, coincidenti col dato grezzo.</t>
+          <t>P.IVA 01118460474, 10-19 dipendenti. Indirizzo e telefono confermati da fonte indipendente, coincidenti col dato grezzo. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/output/2026-08-31_12_Italia_Toscana_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-08-31_12_Italia_Toscana_Componentistica_Ventilazione_industriale.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
